--- a/DataRepo/tests/data/accucor_with_multiple_labels/samples_v3.xlsx
+++ b/DataRepo/tests/data/accucor_with_multiple_labels/samples_v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/accucor_with_multiple_labels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/tests/data/accucor_with_multiple_labels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFC6E55-70B9-ED40-B5EE-3F5331DA7D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DD63D8-203A-5D4B-8C2F-9CA2F698FFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="31280" windowHeight="14260" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12500" yWindow="5260" windowWidth="31280" windowHeight="14260" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="Compounds" sheetId="12" r:id="rId12"/>
     <sheet name="LC Protocols" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1877,9 +1877,6 @@
     <t>Liquid chromatography methodology was not provided or is unavailable.</t>
   </si>
   <si>
-    <t>DataRepo/data/tests/accucor_with_multiple_labels/accucor.xlsx</t>
-  </si>
-  <si>
     <t>accucor</t>
   </si>
   <si>
@@ -1986,6 +1983,9 @@
   </si>
   <si>
     <t>No manipulation besides what is already described in other fields.</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/accucor_with_multiple_labels/accucor.xlsx</t>
   </si>
 </sst>
 </file>
@@ -3354,7 +3354,7 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -3659,7 +3659,7 @@
         <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3711,13 +3711,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" t="s">
         <v>173</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>174</v>
-      </c>
-      <c r="D2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3725,83 +3725,83 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" t="s">
         <v>176</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>177</v>
-      </c>
-      <c r="D3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" t="s">
         <v>179</v>
       </c>
-      <c r="B4" t="s">
-        <v>180</v>
-      </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" t="s">
         <v>181</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" t="s">
         <v>182</v>
-      </c>
-      <c r="C5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" t="s">
         <v>184</v>
       </c>
-      <c r="B6" t="s">
-        <v>185</v>
-      </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" t="s">
         <v>186</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" t="s">
         <v>187</v>
-      </c>
-      <c r="C7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" t="s">
         <v>189</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" t="s">
         <v>190</v>
-      </c>
-      <c r="C8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3809,13 +3809,13 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" t="s">
         <v>193</v>
-      </c>
-      <c r="C9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D9" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3823,13 +3823,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" t="s">
         <v>195</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>196</v>
-      </c>
-      <c r="D10" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3837,13 +3837,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" t="s">
         <v>199</v>
-      </c>
-      <c r="C11" t="s">
-        <v>198</v>
-      </c>
-      <c r="D11" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3851,13 +3851,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" t="s">
         <v>202</v>
-      </c>
-      <c r="C12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -5559,13 +5559,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" t="s">
         <v>169</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>170</v>
-      </c>
-      <c r="C2" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -5647,10 +5647,10 @@
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5661,10 +5661,10 @@
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5675,10 +5675,10 @@
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5689,10 +5689,10 @@
         <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
